--- a/src/ii_skills/shared/excel_templates/04_comps_table.xlsx
+++ b/src/ii_skills/shared/excel_templates/04_comps_table.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trading_Comps" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,11 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.0&quot;x&quot;"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,14 +29,24 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="0001395D"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="14"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -47,14 +55,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A4A4A"/>
-        <bgColor rgb="004A4A4A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F0F0F0"/>
-        <bgColor rgb="00F0F0F0"/>
+        <fgColor rgb="0001395D"/>
+        <bgColor rgb="0001395D"/>
       </patternFill>
     </fill>
     <fill>
@@ -73,33 +75,37 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="1" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,352 +471,369 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1"/>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Public Comparable Companies</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>$ in millions, unless otherwise noted</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Mkt_Cap_M</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>EV_M</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>PE_CY</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>PE_NY</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>EV_EBITDA_CY</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>EV_EBITDA_NY</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Is_Subject</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Peer A</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Mkt Cap</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>EV/Rev</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>P/E CY</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>P/E NY</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Rev Growth</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>EBITDA Margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Peer Company A</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>PEER.TO</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>45.5</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="E6" s="5" t="n">
         <v>2450</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="F6" s="5" t="n">
         <v>3100</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>8.5x</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>12.3x</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>18.5</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="J6" t="n">
         <v>16.2</v>
       </c>
-      <c r="H2" s="5" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="J2" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Peer B</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Peer Company B</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>PB.TO</t>
         </is>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="D7" s="4" t="n">
         <v>32.25</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="E7" s="5" t="n">
         <v>1890</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="F7" s="5" t="n">
         <v>2350</v>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>7.2x</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>14.1x</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>21.2</v>
       </c>
-      <c r="G3" s="9" t="n">
+      <c r="J7" t="n">
         <v>18.7</v>
       </c>
-      <c r="H3" s="9" t="n">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Peer Company C</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PC.TO</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>58.75</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>3200</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>4100</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>9.8x</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>13.2x</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Peer Company D</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PD.TO</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6.8x</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>11.8x</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr"/>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Subject Company</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>SUBJ.TO</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>1450</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>1850</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>5.5x</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>10.5x</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="J10" s="7" t="n">
         <v>14.1</v>
       </c>
-      <c r="I3" s="9" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="J3" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Peer C</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>PC.TO</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>58.75</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>3200</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>4100</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J4" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>Subject Co</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>SUBJ.TO</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="n">
-        <v>28</v>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>1450</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>1850</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I5" s="13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J5" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Peer D</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>PD.TO</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>2100</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>2800</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J6" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="H7" s="9" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="I7" s="9" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J7" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Mean</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>8.1x</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12.9x</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Median</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="J8" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>TRADING COMPS TABLE TEMPLATE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Add peer companies with their trading multiples.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Set Is_Subject=TRUE for your company (row will be highlighted green).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Include Average and Median rows at the bottom.</t>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>7.9x</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>12.8x</t>
         </is>
       </c>
     </row>
